--- a/business-libraries/test-data/learning_problem/keyword_route.xlsx
+++ b/business-libraries/test-data/learning_problem/keyword_route.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,16 +448,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>KW_LP_01</v>
+        <v>LP_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>成绩下滑</v>
+        <v>成绩下滑,考砸了,退步</v>
       </c>
       <c r="C2" t="str">
-        <v>成绩下滑相关；工作压力大；感觉疲惫</v>
+        <v>越来越差,跟不上</v>
       </c>
       <c r="D2" t="str">
-        <v>开玩笑的表达；反讽</v>
+        <v/>
       </c>
       <c r="E2" t="str">
         <v>learning_problem</v>
@@ -466,42 +466,42 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>exact</v>
+        <v>fuzzy</v>
       </c>
       <c r="H2" t="str">
-        <v>red</v>
+        <v>yellow</v>
       </c>
       <c r="I2" t="str">
-        <v>成绩下滑</v>
+        <v>学业下降</v>
       </c>
       <c r="J2" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="K2" t="str">
         <v>LP_RX_001</v>
       </c>
       <c r="L2" t="str">
-        <v>未触发红线</v>
+        <v/>
       </c>
       <c r="M2" t="str">
-        <v>1.0</v>
+        <v>0.85</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
       </c>
       <c r="O2" t="str">
-        <v>教师在对话中表达成绩下滑相关信号，触发学生学习问题模块评估和工具推荐</v>
+        <v>学业表现下降信号</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>KW_LP_02</v>
+        <v>LP_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>注意力不集中</v>
+        <v>不写作业,拖着不做,交不上</v>
       </c>
       <c r="C3" t="str">
-        <v>注意力不集中相关；注意力不集中表现</v>
+        <v>作业总是不交,拖延</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -510,22 +510,22 @@
         <v>learning_problem</v>
       </c>
       <c r="F3" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
         <v>fuzzy</v>
       </c>
       <c r="H3" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="I3" t="str">
-        <v>注意力不集中</v>
+        <v>行为失序</v>
       </c>
       <c r="J3" t="str">
-        <v>LP_FIVE_Q</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="K3" t="str">
-        <v>LP_RX_002</v>
+        <v>LP_RX_001</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -537,18 +537,18 @@
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>教师表达注意力不集中相关困扰，推荐对应自我照顾工具</v>
+        <v>学习行为失序信号</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>KW_LP_03</v>
+        <v>LP_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>作业不交</v>
+        <v>听不懂,学不会,不理解</v>
       </c>
       <c r="C4" t="str">
-        <v>作业不交相关；情绪不良</v>
+        <v>讲了也不会,一变就不会</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -557,45 +557,45 @@
         <v>learning_problem</v>
       </c>
       <c r="F4" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G4" t="str">
         <v>fuzzy</v>
       </c>
       <c r="H4" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="I4" t="str">
-        <v>作业不交</v>
+        <v>认知困难</v>
       </c>
       <c r="J4" t="str">
-        <v>LP_QUICK</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="K4" t="str">
-        <v>LP_RX_003</v>
+        <v>LP_RX_002</v>
       </c>
       <c r="L4" t="str">
-        <v>未触发红线</v>
+        <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
       </c>
       <c r="O4" t="str">
-        <v>教师表达作业不交相关信号，推荐同伴支持或自评</v>
+        <v>认知层困难信号</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>KW_LP_04</v>
+        <v>LP_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>上课走神</v>
+        <v>不想学,没兴趣,懒得学</v>
       </c>
       <c r="C5" t="str">
-        <v>上课走神相关；无精打采</v>
+        <v>不上心,提不起劲</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -604,7 +604,7 @@
         <v>learning_problem</v>
       </c>
       <c r="F5" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G5" t="str">
         <v>fuzzy</v>
@@ -613,30 +613,77 @@
         <v>yellow</v>
       </c>
       <c r="I5" t="str">
-        <v>上课走神</v>
+        <v>动机不足</v>
       </c>
       <c r="J5" t="str">
-        <v>LP_QUICK</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="K5" t="str">
-        <v>LP_RX_004</v>
+        <v>LP_RX_005</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="N5" t="str">
         <v>always</v>
       </c>
       <c r="O5" t="str">
-        <v>教师表达上课走神相关信号，推荐认知类工具</v>
+        <v>学习动机不足信号</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>LP_KW_05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>我就是学不会,笨,没救了</v>
+      </c>
+      <c r="C6" t="str">
+        <v>再努力也没用,放弃了</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F6" t="str">
+        <v>5</v>
+      </c>
+      <c r="G6" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H6" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I6" t="str">
+        <v>习得性无助</v>
+      </c>
+      <c r="J6" t="str">
+        <v>LP_MOTIVATION</v>
+      </c>
+      <c r="K6" t="str">
+        <v>LP_RX_006</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v>0.9</v>
+      </c>
+      <c r="N6" t="str">
+        <v>always</v>
+      </c>
+      <c r="O6" t="str">
+        <v>习得性无助信号</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/business-libraries/test-data/learning_problem/keyword_route.xlsx
+++ b/business-libraries/test-data/learning_problem/keyword_route.xlsx
@@ -451,10 +451,10 @@
         <v>LP_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>成绩下滑,考砸了,退步</v>
+        <v>成绩下滑;考砸了;退步</v>
       </c>
       <c r="C2" t="str">
-        <v>越来越差,跟不上</v>
+        <v>越来越差;跟不上</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -475,16 +475,16 @@
         <v>学业下降</v>
       </c>
       <c r="J2" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="K2" t="str">
-        <v>LP_RX_001</v>
+        <v>LP_RX_01</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
@@ -498,10 +498,10 @@
         <v>LP_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>不写作业,拖着不做,交不上</v>
+        <v>不写作业;拖着不做;交不上</v>
       </c>
       <c r="C3" t="str">
-        <v>作业总是不交,拖延</v>
+        <v>作业总是不交;拖延</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -522,10 +522,10 @@
         <v>行为失序</v>
       </c>
       <c r="J3" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="K3" t="str">
-        <v>LP_RX_001</v>
+        <v>LP_RX_01</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -545,10 +545,10 @@
         <v>LP_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>听不懂,学不会,不理解</v>
+        <v>听不懂;学不会;不理解</v>
       </c>
       <c r="C4" t="str">
-        <v>讲了也不会,一变就不会</v>
+        <v>讲了也不会;一变就不会</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -569,16 +569,16 @@
         <v>认知困难</v>
       </c>
       <c r="J4" t="str">
-        <v>LP_THREE_LAYER</v>
+        <v>LP_S1</v>
       </c>
       <c r="K4" t="str">
-        <v>LP_RX_002</v>
+        <v>LP_RX_02</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
@@ -592,10 +592,10 @@
         <v>LP_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>不想学,没兴趣,懒得学</v>
+        <v>不想学;没兴趣;懒得学</v>
       </c>
       <c r="C5" t="str">
-        <v>不上心,提不起劲</v>
+        <v>不上心;提不起劲</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -616,16 +616,16 @@
         <v>动机不足</v>
       </c>
       <c r="J5" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="K5" t="str">
-        <v>LP_RX_005</v>
+        <v>LP_RX_05</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="N5" t="str">
         <v>always</v>
@@ -639,10 +639,10 @@
         <v>LP_KW_05</v>
       </c>
       <c r="B6" t="str">
-        <v>我就是学不会,笨,没救了</v>
+        <v>我就是学不会;笨;没救了</v>
       </c>
       <c r="C6" t="str">
-        <v>再努力也没用,放弃了</v>
+        <v>再努力也没用;放弃了</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -663,16 +663,16 @@
         <v>习得性无助</v>
       </c>
       <c r="J6" t="str">
-        <v>LP_MOTIVATION</v>
+        <v>LP_S2</v>
       </c>
       <c r="K6" t="str">
-        <v>LP_RX_006</v>
+        <v>LP_RX_06</v>
       </c>
       <c r="L6" t="str">
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N6" t="str">
         <v>always</v>

--- a/business-libraries/test-data/learning_problem/keyword_route.xlsx
+++ b/business-libraries/test-data/learning_problem/keyword_route.xlsx
@@ -451,10 +451,10 @@
         <v>LP_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>成绩下滑;考砸了;退步</v>
+        <v>成绩下滑,考砸了,退步</v>
       </c>
       <c r="C2" t="str">
-        <v>越来越差;跟不上</v>
+        <v>越来越差,跟不上</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -475,16 +475,16 @@
         <v>学业下降</v>
       </c>
       <c r="J2" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="K2" t="str">
-        <v>LP_RX_01</v>
+        <v>LP_RX_001</v>
       </c>
       <c r="L2" t="str">
         <v/>
       </c>
       <c r="M2" t="str">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="N2" t="str">
         <v>always</v>
@@ -498,10 +498,10 @@
         <v>LP_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>不写作业;拖着不做;交不上</v>
+        <v>不写作业,拖着不做,交不上</v>
       </c>
       <c r="C3" t="str">
-        <v>作业总是不交;拖延</v>
+        <v>作业总是不交,拖延</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -522,10 +522,10 @@
         <v>行为失序</v>
       </c>
       <c r="J3" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="K3" t="str">
-        <v>LP_RX_01</v>
+        <v>LP_RX_001</v>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -545,10 +545,10 @@
         <v>LP_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>听不懂;学不会;不理解</v>
+        <v>听不懂,学不会,不理解</v>
       </c>
       <c r="C4" t="str">
-        <v>讲了也不会;一变就不会</v>
+        <v>讲了也不会,一变就不会</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -569,16 +569,16 @@
         <v>认知困难</v>
       </c>
       <c r="J4" t="str">
-        <v>LP_S1</v>
+        <v>LP_THREE_LAYER</v>
       </c>
       <c r="K4" t="str">
-        <v>LP_RX_02</v>
+        <v>LP_RX_002</v>
       </c>
       <c r="L4" t="str">
         <v/>
       </c>
       <c r="M4" t="str">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="N4" t="str">
         <v>always</v>
@@ -592,10 +592,10 @@
         <v>LP_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>不想学;没兴趣;懒得学</v>
+        <v>不想学,没兴趣,懒得学</v>
       </c>
       <c r="C5" t="str">
-        <v>不上心;提不起劲</v>
+        <v>不上心,提不起劲</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -616,16 +616,16 @@
         <v>动机不足</v>
       </c>
       <c r="J5" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="K5" t="str">
-        <v>LP_RX_05</v>
+        <v>LP_RX_005</v>
       </c>
       <c r="L5" t="str">
         <v/>
       </c>
       <c r="M5" t="str">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="N5" t="str">
         <v>always</v>
@@ -639,10 +639,10 @@
         <v>LP_KW_05</v>
       </c>
       <c r="B6" t="str">
-        <v>我就是学不会;笨;没救了</v>
+        <v>我就是学不会,笨,没救了</v>
       </c>
       <c r="C6" t="str">
-        <v>再努力也没用;放弃了</v>
+        <v>再努力也没用,放弃了</v>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -663,16 +663,16 @@
         <v>习得性无助</v>
       </c>
       <c r="J6" t="str">
-        <v>LP_S2</v>
+        <v>LP_MOTIVATION</v>
       </c>
       <c r="K6" t="str">
-        <v>LP_RX_06</v>
+        <v>LP_RX_006</v>
       </c>
       <c r="L6" t="str">
         <v/>
       </c>
       <c r="M6" t="str">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N6" t="str">
         <v>always</v>

--- a/business-libraries/test-data/learning_problem/keyword_route.xlsx
+++ b/business-libraries/test-data/learning_problem/keyword_route.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -451,10 +451,10 @@
         <v>LP_KW_01</v>
       </c>
       <c r="B2" t="str">
-        <v>成绩下滑;考砸了;退步</v>
+        <v>走神;分心;坐不住;多动</v>
       </c>
       <c r="C2" t="str">
-        <v>越来越差;跟不上</v>
+        <v>注意力不集中;上课走神;静不下来</v>
       </c>
       <c r="D2" t="str">
         <v/>
@@ -472,13 +472,13 @@
         <v>yellow</v>
       </c>
       <c r="I2" t="str">
-        <v>学业下降</v>
+        <v>注意力</v>
       </c>
       <c r="J2" t="str">
         <v>LP_S1</v>
       </c>
       <c r="K2" t="str">
-        <v>LP_RX_01</v>
+        <v>LP_RX_04</v>
       </c>
       <c r="L2" t="str">
         <v/>
@@ -490,7 +490,7 @@
         <v>always</v>
       </c>
       <c r="O2" t="str">
-        <v>学业表现下降信号</v>
+        <v>注意力与多动信号，引导 SNAP-IV 筛查</v>
       </c>
     </row>
     <row r="3">
@@ -498,10 +498,10 @@
         <v>LP_KW_02</v>
       </c>
       <c r="B3" t="str">
-        <v>不写作业;拖着不做;交不上</v>
+        <v>ADHD;多动症;注意缺陷</v>
       </c>
       <c r="C3" t="str">
-        <v>作业总是不交;拖延</v>
+        <v/>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -513,19 +513,19 @@
         <v>2</v>
       </c>
       <c r="G3" t="str">
-        <v>fuzzy</v>
+        <v>exact</v>
       </c>
       <c r="H3" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="I3" t="str">
-        <v>行为失序</v>
+        <v>注意力</v>
       </c>
       <c r="J3" t="str">
         <v>LP_S1</v>
       </c>
       <c r="K3" t="str">
-        <v>LP_RX_01</v>
+        <v/>
       </c>
       <c r="L3" t="str">
         <v/>
@@ -537,7 +537,7 @@
         <v>always</v>
       </c>
       <c r="O3" t="str">
-        <v>学习行为失序信号</v>
+        <v>ADHD 相关表述，引导筛查并提示专业评估</v>
       </c>
     </row>
     <row r="4">
@@ -545,10 +545,10 @@
         <v>LP_KW_03</v>
       </c>
       <c r="B4" t="str">
-        <v>听不懂;学不会;不理解</v>
+        <v>作业拖拉;拖延;不交作业;磨蹭</v>
       </c>
       <c r="C4" t="str">
-        <v>讲了也不会;一变就不会</v>
+        <v>作业总是不交;拖着不做</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -563,13 +563,13 @@
         <v>fuzzy</v>
       </c>
       <c r="H4" t="str">
-        <v>orange</v>
+        <v>yellow</v>
       </c>
       <c r="I4" t="str">
-        <v>认知困难</v>
+        <v>学习行为</v>
       </c>
       <c r="J4" t="str">
-        <v>LP_S1</v>
+        <v>LP_S6</v>
       </c>
       <c r="K4" t="str">
         <v>LP_RX_02</v>
@@ -584,7 +584,7 @@
         <v>always</v>
       </c>
       <c r="O4" t="str">
-        <v>认知层困难信号</v>
+        <v>作业与学习行为信号</v>
       </c>
     </row>
     <row r="5">
@@ -592,10 +592,10 @@
         <v>LP_KW_04</v>
       </c>
       <c r="B5" t="str">
-        <v>不想学;没兴趣;懒得学</v>
+        <v>偏科;瘸腿;成绩下滑;退步</v>
       </c>
       <c r="C5" t="str">
-        <v>不上心;提不起劲</v>
+        <v>越来越差;跟不上</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -610,16 +610,16 @@
         <v>fuzzy</v>
       </c>
       <c r="H5" t="str">
-        <v>yellow</v>
+        <v>orange</v>
       </c>
       <c r="I5" t="str">
-        <v>动机不足</v>
+        <v>学业表现</v>
       </c>
       <c r="J5" t="str">
-        <v>LP_S2</v>
+        <v>LP_S7</v>
       </c>
       <c r="K5" t="str">
-        <v>LP_RX_05</v>
+        <v>LP_RX_16</v>
       </c>
       <c r="L5" t="str">
         <v/>
@@ -631,7 +631,7 @@
         <v>always</v>
       </c>
       <c r="O5" t="str">
-        <v>学习动机不足信号</v>
+        <v>成绩薄弱与偏科信号</v>
       </c>
     </row>
     <row r="6">
@@ -639,10 +639,10 @@
         <v>LP_KW_05</v>
       </c>
       <c r="B6" t="str">
-        <v>我就是学不会;笨;没救了</v>
+        <v>三年级;突然变差;断层</v>
       </c>
       <c r="C6" t="str">
-        <v>再努力也没用;放弃了</v>
+        <v/>
       </c>
       <c r="D6" t="str">
         <v/>
@@ -657,33 +657,597 @@
         <v>fuzzy</v>
       </c>
       <c r="H6" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I6" t="str">
+        <v>学业表现</v>
+      </c>
+      <c r="J6" t="str">
+        <v>LP_S7</v>
+      </c>
+      <c r="K6" t="str">
+        <v>LP_RX_16</v>
+      </c>
+      <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N6" t="str">
+        <v>always</v>
+      </c>
+      <c r="O6" t="str">
+        <v>三年级现象与知识断层信号</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>LP_KW_06</v>
+      </c>
+      <c r="B7" t="str">
+        <v>听不懂;记不住;学不会</v>
+      </c>
+      <c r="C7" t="str">
+        <v>讲了也不会;一变就不会</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F7" t="str">
+        <v>6</v>
+      </c>
+      <c r="G7" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H7" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I7" t="str">
+        <v>学习策略</v>
+      </c>
+      <c r="J7" t="str">
+        <v>LP_S2</v>
+      </c>
+      <c r="K7" t="str">
+        <v>LP_RX_09</v>
+      </c>
+      <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N7" t="str">
+        <v>always</v>
+      </c>
+      <c r="O7" t="str">
+        <v>策略缺失信号</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>LP_KW_07</v>
+      </c>
+      <c r="B8" t="str">
+        <v>不想学;没兴趣;厌学;敷衍</v>
+      </c>
+      <c r="C8" t="str">
+        <v>懒得学;提不起劲</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F8" t="str">
+        <v>7</v>
+      </c>
+      <c r="G8" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H8" t="str">
         <v>orange</v>
       </c>
-      <c r="I6" t="str">
-        <v>习得性无助</v>
-      </c>
-      <c r="J6" t="str">
+      <c r="I8" t="str">
+        <v>学习动机</v>
+      </c>
+      <c r="J8" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="K8" t="str">
+        <v>LP_RX_08</v>
+      </c>
+      <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N8" t="str">
+        <v>always</v>
+      </c>
+      <c r="O8" t="str">
+        <v>学习动机缺失信号</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>LP_KW_08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>考试紧张;考试焦虑;怕考试</v>
+      </c>
+      <c r="C9" t="str">
+        <v>考前睡不着;考砸了</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F9" t="str">
+        <v>8</v>
+      </c>
+      <c r="G9" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H9" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I9" t="str">
+        <v>学业情绪</v>
+      </c>
+      <c r="J9" t="str">
+        <v>LP_S4</v>
+      </c>
+      <c r="K9" t="str">
+        <v>LP_RX_32</v>
+      </c>
+      <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N9" t="str">
+        <v>always</v>
+      </c>
+      <c r="O9" t="str">
+        <v>考试焦虑信号</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>LP_KW_09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>我就是学不会;我很笨;没救了</v>
+      </c>
+      <c r="C10" t="str">
+        <v>再努力也没用;放弃了</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F10" t="str">
+        <v>9</v>
+      </c>
+      <c r="G10" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H10" t="str">
+        <v>orange</v>
+      </c>
+      <c r="I10" t="str">
+        <v>自我效能</v>
+      </c>
+      <c r="J10" t="str">
+        <v>LP_S3</v>
+      </c>
+      <c r="K10" t="str">
+        <v>LP_RX_10</v>
+      </c>
+      <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N10" t="str">
+        <v>always</v>
+      </c>
+      <c r="O10" t="str">
+        <v>习得性无助与效能感不足信号</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>LP_KW_10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>和爸妈关系;不跟爸妈说;怕父母;亲子</v>
+      </c>
+      <c r="C11" t="str">
+        <v>和家里闹矛盾</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F11" t="str">
+        <v>10</v>
+      </c>
+      <c r="G11" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H11" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I11" t="str">
+        <v>亲子关系</v>
+      </c>
+      <c r="J11" t="str">
+        <v>LP_S5</v>
+      </c>
+      <c r="K11" t="str">
+        <v>LP_RX_11</v>
+      </c>
+      <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N11" t="str">
+        <v>always</v>
+      </c>
+      <c r="O11" t="str">
+        <v>亲子依恋相关信号</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>LP_KW_11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>上课状态;课堂表现;听讲</v>
+      </c>
+      <c r="C12" t="str">
+        <v>上课不听;课堂纪律</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F12" t="str">
+        <v>11</v>
+      </c>
+      <c r="G12" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H12" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I12" t="str">
+        <v>课堂行为</v>
+      </c>
+      <c r="J12" t="str">
+        <v>LP_S6</v>
+      </c>
+      <c r="K12" t="str">
+        <v>LP_RX_02</v>
+      </c>
+      <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N12" t="str">
+        <v>always</v>
+      </c>
+      <c r="O12" t="str">
+        <v>课堂行为观察信号</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>LP_KW_12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>被孤立;没朋友;同伴排斥</v>
+      </c>
+      <c r="C13" t="str">
+        <v>被同学欺负;不敢交朋友</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F13" t="str">
+        <v>12</v>
+      </c>
+      <c r="G13" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H13" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I13" t="str">
+        <v>同伴关系</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>LP_RX_41</v>
+      </c>
+      <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N13" t="str">
+        <v>always</v>
+      </c>
+      <c r="O13" t="str">
+        <v>同伴关系问题信号</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>LP_KW_13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>怕老师;和老师关系</v>
+      </c>
+      <c r="C14" t="str">
+        <v>不敢问老师</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F14" t="str">
+        <v>13</v>
+      </c>
+      <c r="G14" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H14" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I14" t="str">
+        <v>师生关系</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>LP_RX_18</v>
+      </c>
+      <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N14" t="str">
+        <v>always</v>
+      </c>
+      <c r="O14" t="str">
+        <v>师生关系紧张信号</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>LP_KW_14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>家庭;父母吵架;家里影响</v>
+      </c>
+      <c r="C15" t="str">
+        <v>家里没人管;家长太严</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F15" t="str">
+        <v>14</v>
+      </c>
+      <c r="G15" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H15" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I15" t="str">
+        <v>家庭环境</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>LP_RX_03</v>
+      </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N15" t="str">
+        <v>always</v>
+      </c>
+      <c r="O15" t="str">
+        <v>家庭因素参与学习问题信号</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>LP_KW_15</v>
+      </c>
+      <c r="B16" t="str">
+        <v>小组;项目;合作困难</v>
+      </c>
+      <c r="C16" t="str">
+        <v>组里推诿;没人干活</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F16" t="str">
+        <v>15</v>
+      </c>
+      <c r="G16" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H16" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I16" t="str">
+        <v>六力特色</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>LP_RX_06</v>
+      </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N16" t="str">
+        <v>always</v>
+      </c>
+      <c r="O16" t="str">
+        <v>项目化小组协作问题信号</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>LP_KW_16</v>
+      </c>
+      <c r="B17" t="str">
+        <v>思维乱;逻辑不清;不会思考</v>
+      </c>
+      <c r="C17" t="str">
+        <v>一听就懂一做就错</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F17" t="str">
+        <v>16</v>
+      </c>
+      <c r="G17" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H17" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I17" t="str">
+        <v>六力特色</v>
+      </c>
+      <c r="J17" t="str">
         <v>LP_S2</v>
       </c>
-      <c r="K6" t="str">
-        <v>LP_RX_06</v>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="N6" t="str">
-        <v>always</v>
-      </c>
-      <c r="O6" t="str">
-        <v>习得性无助信号</v>
+      <c r="K17" t="str">
+        <v>LP_RX_05</v>
+      </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N17" t="str">
+        <v>always</v>
+      </c>
+      <c r="O17" t="str">
+        <v>元系统思维薄弱信号</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>LP_KW_17</v>
+      </c>
+      <c r="B18" t="str">
+        <v>手机;屏幕;晚睡;睡眠</v>
+      </c>
+      <c r="C18" t="str">
+        <v>玩手机;熬夜</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v>learning_problem</v>
+      </c>
+      <c r="F18" t="str">
+        <v>17</v>
+      </c>
+      <c r="G18" t="str">
+        <v>fuzzy</v>
+      </c>
+      <c r="H18" t="str">
+        <v>yellow</v>
+      </c>
+      <c r="I18" t="str">
+        <v>生活习惯</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>LP_RX_03</v>
+      </c>
+      <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="N18" t="str">
+        <v>always</v>
+      </c>
+      <c r="O18" t="str">
+        <v>生活习惯风险因素</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O18"/>
   </ignoredErrors>
 </worksheet>
 </file>